--- a/data/trans_orig/IP40A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP40A-Clase-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45631</t>
+          <t>44579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>21462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>28367</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55294</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47966</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31315</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -3908,92 +3908,92 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
           <t>3820</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>3830</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>31080</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>23493</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>48224</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>57821</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>82568</t>
+          <t>82265</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>67173</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>90507</t>
+          <t>89383</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>54971</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>76005</t>
+          <t>75735</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>129573</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>160624</t>
+          <t>158990</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33093</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52603</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>47380</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>93844</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>23814</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,82 +5508,82 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>7771</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3552</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>7100</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5832,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>57323</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>53658</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>80867</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>105626</t>
+          <t>105527</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>52459</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>66745</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>90863</t>
+          <t>91832</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>32963</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>55255</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7761,12 +7761,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>34421</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>41213</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>40788</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>61704</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>78763</t>
+          <t>77393</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>99910</t>
+          <t>99447</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>132783</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>89037</t>
+          <t>90457</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>118953</t>
+          <t>120576</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>96359</t>
+          <t>96635</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>127879</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>193943</t>
+          <t>196006</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>239430</t>
+          <t>239307</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>187821</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>224860</t>
+          <t>226340</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>167595</t>
+          <t>167340</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>202443</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>364536</t>
+          <t>365961</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>417259</t>
+          <t>417771</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>92303</t>
+          <t>92519</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>123794</t>
+          <t>123950</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>84159</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>113615</t>
+          <t>115233</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>182725</t>
+          <t>185606</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>224952</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>32151</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8439,12 +8439,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8489,12 +8489,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -9016,12 +9016,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -9129,12 +9129,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41451</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -9355,12 +9355,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19731</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -9468,12 +9468,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>31213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -10263,12 +10263,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -10376,12 +10376,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10411,12 +10411,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10524,12 +10524,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10559,12 +10559,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -10602,12 +10602,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10652,12 +10652,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10672,12 +10672,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69594</t>
+          <t>68926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10750,12 +10750,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10785,12 +10785,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>26900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10843,12 +10843,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10898,12 +10898,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -11397,12 +11397,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -11510,12 +11510,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11525,12 +11525,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11673,12 +11673,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -11849,12 +11849,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11899,12 +11899,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11997,12 +11997,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12012,12 +12012,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12110,12 +12110,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12125,12 +12125,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -12531,12 +12531,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12546,12 +12546,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12566,12 +12566,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12601,12 +12601,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -12644,12 +12644,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12679,12 +12679,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12714,12 +12714,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12757,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12772,12 +12772,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>46807</t>
+          <t>46017</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12807,12 +12807,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>57693</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>81039</t>
+          <t>81108</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>69757</t>
+          <t>69403</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>70210</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>105292</t>
+          <t>104650</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>134075</t>
+          <t>134102</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -12983,12 +12983,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>37530</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>56845</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -13053,12 +13053,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>84977</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>112246</t>
+          <t>112123</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -13068,12 +13068,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16134</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31689</t>
+          <t>31201</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -13209,12 +13209,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -13229,77 +13229,77 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>6532</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>8785</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>6646</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>4443</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>9390</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -13778,12 +13778,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -13891,12 +13891,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -13926,12 +13926,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>26374</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -14004,12 +14004,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -14039,12 +14039,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -14054,12 +14054,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>48489</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>69224</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>40569</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>56809</t>
+          <t>56943</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>60516</t>
+          <t>60970</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>87222</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>113504</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -14202,12 +14202,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14230,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -14245,12 +14245,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -14300,12 +14300,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -14343,12 +14343,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -14413,12 +14413,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -14428,12 +14428,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>786</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14884,12 +14884,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -14912,12 +14912,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14927,12 +14927,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14982,12 +14982,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14997,12 +14997,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -15040,12 +15040,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15075,12 +15075,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -15138,12 +15138,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25070</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -15173,12 +15173,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -15208,12 +15208,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -15223,12 +15223,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -15251,12 +15251,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16954</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -15286,12 +15286,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -15336,12 +15336,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -15364,12 +15364,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -15399,12 +15399,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -15434,12 +15434,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -15449,12 +15449,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -15547,12 +15547,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -15707,12 +15707,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -15777,12 +15777,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -15792,12 +15792,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -15820,12 +15820,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15890,12 +15890,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -15933,12 +15933,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15968,12 +15968,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -15983,12 +15983,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -16003,12 +16003,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>54724</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -16046,12 +16046,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -16061,12 +16061,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -16081,12 +16081,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>70246</t>
+          <t>70444</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -16096,12 +16096,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>93770</t>
+          <t>92664</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>125311</t>
+          <t>125085</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -16159,12 +16159,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>98390</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16194,12 +16194,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>90763</t>
+          <t>89121</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>121695</t>
+          <t>121838</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -16209,12 +16209,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -16229,12 +16229,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>171358</t>
+          <t>170144</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>212684</t>
+          <t>211679</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -16272,12 +16272,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>150614</t>
+          <t>149659</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>182874</t>
+          <t>183666</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -16307,12 +16307,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>156101</t>
+          <t>154815</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>191888</t>
+          <t>192493</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>315454</t>
+          <t>314332</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>365150</t>
+          <t>365840</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>120453</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>152409</t>
+          <t>153301</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -16400,12 +16400,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -16420,12 +16420,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>125800</t>
+          <t>127356</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>160465</t>
+          <t>162951</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -16435,12 +16435,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>257206</t>
+          <t>256939</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>303035</t>
+          <t>306097</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -16498,12 +16498,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>25068</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>30760</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>51533</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -16568,12 +16568,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>60544</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>87960</t>
+          <t>87732</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -16611,12 +16611,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -16626,12 +16626,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -16661,12 +16661,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -16681,12 +16681,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
